--- a/Assets/StreamingAssets/Localization/UI.xlsx
+++ b/Assets/StreamingAssets/Localization/UI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\IdleProject\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3E56C8-23A4-4211-8833-571DCB30EF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE81DC6-C1AB-489D-9FF8-569DEABBD2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>key</t>
   </si>
@@ -52,6 +52,30 @@
   </si>
   <si>
     <t>Ур.</t>
+  </si>
+  <si>
+    <t>Взаимодействие</t>
+  </si>
+  <si>
+    <t>interact</t>
+  </si>
+  <si>
+    <t>Interaction</t>
+  </si>
+  <si>
+    <t>sec</t>
+  </si>
+  <si>
+    <t>сек</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>МАКС</t>
   </si>
 </sst>
 </file>
@@ -384,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
@@ -426,6 +450,39 @@
         <v>8</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/StreamingAssets/Localization/UI.xlsx
+++ b/Assets/StreamingAssets/Localization/UI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\IdleProject\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE81DC6-C1AB-489D-9FF8-569DEABBD2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587C9402-D0C6-46FC-B8E0-28DA5AE21BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>key</t>
   </si>
@@ -76,6 +76,15 @@
   </si>
   <si>
     <t>МАКС</t>
+  </si>
+  <si>
+    <t>upgrade_flame</t>
+  </si>
+  <si>
+    <t>Upgrade Flame</t>
+  </si>
+  <si>
+    <t>Улучшить Факел</t>
   </si>
 </sst>
 </file>
@@ -408,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
@@ -483,6 +492,17 @@
         <v>13</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/StreamingAssets/Localization/UI.xlsx
+++ b/Assets/StreamingAssets/Localization/UI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\IdleProject\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587C9402-D0C6-46FC-B8E0-28DA5AE21BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB12EB8-92E4-4D2D-9B84-79DFDA2F95E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>key</t>
   </si>
@@ -72,12 +72,6 @@
     <t>max</t>
   </si>
   <si>
-    <t>MAX</t>
-  </si>
-  <si>
-    <t>МАКС</t>
-  </si>
-  <si>
     <t>upgrade_flame</t>
   </si>
   <si>
@@ -85,13 +79,73 @@
   </si>
   <si>
     <t>Улучшить Факел</t>
+  </si>
+  <si>
+    <t>requirement_altar_level</t>
+  </si>
+  <si>
+    <t>upgrade_building</t>
+  </si>
+  <si>
+    <t>Upgrade Building</t>
+  </si>
+  <si>
+    <t>Улучшить Здание</t>
+  </si>
+  <si>
+    <t>requirement_building_level</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Макс.</t>
+  </si>
+  <si>
+    <t>Требуется уровень Здания</t>
+  </si>
+  <si>
+    <t>upgrade_button</t>
+  </si>
+  <si>
+    <t>Upgrade</t>
+  </si>
+  <si>
+    <t>Улучшить</t>
+  </si>
+  <si>
+    <t>Altar level required</t>
+  </si>
+  <si>
+    <t>Требуется уровень Алтаря</t>
+  </si>
+  <si>
+    <t>Building level required</t>
+  </si>
+  <si>
+    <t>Требования не выполнены</t>
+  </si>
+  <si>
+    <t>Requirements not met</t>
+  </si>
+  <si>
+    <t>upgrade_button_requirements_not_met</t>
+  </si>
+  <si>
+    <t>max_level</t>
+  </si>
+  <si>
+    <t>Max level</t>
+  </si>
+  <si>
+    <t>Макс. Уровень</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +161,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,12 +188,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -417,16 +479,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.77734375" style="1" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -437,7 +499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -448,7 +510,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -459,48 +521,114 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>19</v>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/UI.xlsx
+++ b/Assets/StreamingAssets/Localization/UI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\IdleProject\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB12EB8-92E4-4D2D-9B84-79DFDA2F95E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047DDAF0-24BF-4B18-9C0E-AC3AE172F947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>key</t>
   </si>
@@ -139,6 +139,33 @@
   </si>
   <si>
     <t>Макс. Уровень</t>
+  </si>
+  <si>
+    <t>workers</t>
+  </si>
+  <si>
+    <t>Workers</t>
+  </si>
+  <si>
+    <t>Работники</t>
+  </si>
+  <si>
+    <t>per_worker</t>
+  </si>
+  <si>
+    <t>Per Worker</t>
+  </si>
+  <si>
+    <t>Одним Работником</t>
+  </si>
+  <si>
+    <t>total_production</t>
+  </si>
+  <si>
+    <t>Всего</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -479,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.109375" style="1" customWidth="1"/>
@@ -631,6 +658,39 @@
         <v>32</v>
       </c>
     </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
